--- a/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/Test Results/Excel/Automation_Test_Report.xlsx
@@ -30907,7 +30907,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.04s</t>
         </is>
       </c>
     </row>
